--- a/ig/ch-core/StructureDefinition-ch-core-epr-consent.xlsx
+++ b/ig/ch-core/StructureDefinition-ch-core-epr-consent.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>6.0.0</t>
+    <t>7.0.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-16T08:02:49+00:00</t>
+    <t>2026-06-10T15:05:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1055,6 +1055,7 @@
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
   &lt;coding&gt;
     &lt;system value="http://terminology.hl7.org/CodeSystem/consentpolicycodes"/&gt;
+    &lt;version value="3.0.1"/&gt;
     &lt;code value="ch-epr"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
